--- a/docs/EchoMind_Audit_2026-10-14_Project2/00_Evidence_Index.xlsx
+++ b/docs/EchoMind_Audit_2026-10-14_Project2/00_Evidence_Index.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retrieve before the session" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evidence index'!$A$4:$F$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evidence index'!$A$4:$F$100</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Retrieve before the session'!$A$4:$C$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -714,32 +714,32 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>02_Project_Plan</t>
+          <t>01_Contract_Review</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Jira board summary (project plan)</t>
+          <t>EM26-28 Contract Review Record</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>01_Contract_Review/EM26-28_Contract_Review_Record.docx</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Jira timeline</t>
+          <t>Jira board summary (project plan)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Jira board</t>
+          <t>Jira timeline</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -820,12 +820,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>SDLC project plan, roadmap and editions (Jun 2025 → Jul 2026)</t>
+          <t>Jira board</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Scheduling review SCH-1.0 (May–Sep 2025)</t>
+          <t>SDLC project plan, roadmap and editions (Jun 2025 → Jul 2026)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -879,27 +879,27 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>EM26-12 Scheduling review (milestones, schedule risks)</t>
+          <t>Scheduling review SCH-1.0 (May–Sep 2025)</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>02_Project_Plan/2026_EchoMind_Enterprise/EM26-12_Scheduling_Review.docx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/tree/main/docs/qms/evidence-2026/12_Scheduling_Review</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>EM26-12 SDLC record (actual timeline, commits by month)</t>
+          <t>EM26-12 Scheduling review (milestones, schedule risks)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>02_Project_Plan/2026_EchoMind_Enterprise/EM26-12_SDLC_Record.xlsx</t>
+          <t>02_Project_Plan/2026_EchoMind_Enterprise/EM26-12_Scheduling_Review.docx</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Evidence pack</t>
+          <t>https://github.com/RW2523/echomind-enterprise/tree/main/docs/qms/evidence-2026/12_Scheduling_Review</t>
         </is>
       </c>
     </row>
@@ -948,22 +948,22 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>EM26-22 Product roadmap 2025 → 2027 (timeline, plan vs actual, versions, forward plan)</t>
+          <t>EM26-12 SDLC record (actual timeline, commits by month)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>02_Project_Plan/2026_EchoMind_Enterprise/EM26-22_Product_Roadmap.xlsx</t>
+          <t>02_Project_Plan/2026_EchoMind_Enterprise/EM26-12_SDLC_Record.xlsx</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Controlled copy</t>
+          <t>Evidence pack</t>
         </is>
       </c>
     </row>
@@ -980,54 +980,54 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>EM26-23 Project Plan — EchoMind Enterprise</t>
+          <t>EM26-22 Product roadmap 2025 → 2027 (timeline, plan vs actual, versions, forward plan)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>02_Project_Plan/2026_EchoMind_Enterprise/EM26-23_Project_Plan_EchoMind_Enterprise.docx</t>
+          <t>02_Project_Plan/2026_EchoMind_Enterprise/EM26-22_Product_Roadmap.xlsx</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Controlled copy</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>03_Communication_with_Client</t>
+          <t>02_Project_Plan</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Project documentation — EMD-02 (PO delay follow-up, August kick-off), EMD-12 (shipping confirmation and tracking)</t>
+          <t>EM26-23 Project Plan — EchoMind Enterprise</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>2025-07 → 09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>02_Project_Plan/2026_EchoMind_Enterprise/EM26-23_Project_Plan_EchoMind_Enterprise.docx</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Deliverables review DR-1.0 — reviews held with the project lead</t>
+          <t>Project documentation — EMD-02 (PO delay follow-up, August kick-off), EMD-12 (shipping confirmation and tracking)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-07 → 09</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1071,27 +1071,27 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-02 — client feedback</t>
+          <t>Deliverables review DR-1.0 — reviews held with the project lead</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>03_Communication_with_Client/2026_EchoMind_Enterprise/CR-2026-02_Requirements_Client_A_Client_B_Bahrain.docx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Evidence Library</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-03 — client feedback</t>
+          <t>Review record CR-2026-02 — client feedback</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>03_Communication_with_Client/2026_EchoMind_Enterprise/CR-2026-03_Conversation_assistance_v1_Kyutai_Unmute_stack.docx</t>
+          <t>03_Communication_with_Client/2026_EchoMind_Enterprise/CR-2026-02_Requirements_Client_A_Client_B_Bahrain.docx</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-04 — client feedback</t>
+          <t>Review record CR-2026-03 — client feedback</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>03_Communication_with_Client/2026_EchoMind_Enterprise/CR-2026-04_Conversation_assistance_v2_NVIDIA_PersonaPlex.docx</t>
+          <t>03_Communication_with_Client/2026_EchoMind_Enterprise/CR-2026-03_Conversation_assistance_v1_Kyutai_Unmute_stack.docx</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-06 — client feedback</t>
+          <t>Review record CR-2026-04 — client feedback</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>03_Communication_with_Client/2026_EchoMind_Enterprise/CR-2026-06_Live_transcription.docx</t>
+          <t>03_Communication_with_Client/2026_EchoMind_Enterprise/CR-2026-04_Conversation_assistance_v2_NVIDIA_PersonaPlex.docx</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-07 — client feedback</t>
+          <t>Review record CR-2026-06 — client feedback</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>03_Communication_with_Client/2026_EchoMind_Enterprise/CR-2026-07_Conversation_and_live_transcript_demonstration.docx</t>
+          <t>03_Communication_with_Client/2026_EchoMind_Enterprise/CR-2026-06_Live_transcription.docx</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-09 — client feedback</t>
+          <t>Review record CR-2026-07 — client feedback</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>03_Communication_with_Client/2026_EchoMind_Enterprise/CR-2026-09_Document_creation.docx</t>
+          <t>03_Communication_with_Client/2026_EchoMind_Enterprise/CR-2026-07_Conversation_and_live_transcript_demonstration.docx</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1263,59 +1263,59 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>EM26-27 Client Communication Log</t>
+          <t>Review record CR-2026-09 — client feedback</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>03_Communication_with_Client/EM26-27_Client_Communication_Log.xlsx</t>
+          <t>03_Communication_with_Client/2026_EchoMind_Enterprise/CR-2026-09_Document_creation.docx</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Evidence Library</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>04_Requirements</t>
+          <t>03_Communication_with_Client</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Requirements (ECH-QMS-010): fully offline on-premises AI system; BYOA pilot; acceptance by end-to-end test</t>
+          <t>EM26-27 Client Communication Log</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>03_Communication_with_Client/EM26-27_Client_Communication_Log.xlsx</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Acceptance criteria review ACC-1.0</t>
+          <t>Requirements (ECH-QMS-010): fully offline on-premises AI system; BYOA pilot; acceptance by end-to-end test</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -1359,27 +1359,27 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>EM26-17 NFR record and monitoring (2025 finding #6)</t>
+          <t>Acceptance criteria review ACC-1.0</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>04_Requirements/2026_EchoMind_Enterprise/EM26-17_NFR_Record_and_Monitoring.docx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Controlled copy</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -1396,17 +1396,17 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>EM26-20 Functional requirements (39) with traceability</t>
+          <t>EM26-17 NFR record and monitoring (2025 finding #6)</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>04_Requirements/2026_EchoMind_Enterprise/EM26-20_Functional_Requirements.xlsx</t>
+          <t>04_Requirements/2026_EchoMind_Enterprise/EM26-17_NFR_Record_and_Monitoring.docx</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>EM26-21 Non-functional requirements (31 + 9 from 2025) with measurements</t>
+          <t>EM26-20 Functional requirements (39) with traceability</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>04_Requirements/2026_EchoMind_Enterprise/EM26-21_Non_Functional_Requirements.xlsx</t>
+          <t>04_Requirements/2026_EchoMind_Enterprise/EM26-20_Functional_Requirements.xlsx</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1450,39 +1450,39 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>05_Changes_to_Requirements</t>
+          <t>04_Requirements</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>2025 change requests CR-2025-01 … 04 (lessons log)</t>
+          <t>EM26-21 Non-functional requirements (31 + 9 from 2025) with measurements</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2025-05 → 09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>04_Requirements/2026_EchoMind_Enterprise/EM26-21_Non_Functional_Requirements.xlsx</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>Controlled copy</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>05_Changes_to_Requirements</t>
+          <t>04_Requirements</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -1492,22 +1492,22 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-03 — the client feedback that changed the requirement</t>
+          <t>EM26-29 Software Requirements Specification</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/CR-2026-03_Conversation_assistance_v1_Kyutai_Unmute_stack.docx</t>
+          <t>04_Requirements/EM26-29_Software_Requirements_Specification.docx</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Evidence Library</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1519,27 +1519,27 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-04 — the client feedback that changed the requirement</t>
+          <t>2025 change requests CR-2025-01 … 04 (lessons log)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025-05 → 09</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/CR-2026-04_Conversation_assistance_v2_NVIDIA_PersonaPlex.docx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Evidence Library</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-06 — the client feedback that changed the requirement</t>
+          <t>Review record CR-2026-03 — the client feedback that changed the requirement</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/CR-2026-06_Live_transcription.docx</t>
+          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/CR-2026-03_Conversation_assistance_v1_Kyutai_Unmute_stack.docx</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -1588,22 +1588,22 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>REG-07 Design and change register</t>
+          <t>Review record CR-2026-04 — the client feedback that changed the requirement</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/registers__REG-07_Design_and_Change_Register.docx</t>
+          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/CR-2026-04_Conversation_assistance_v2_NVIDIA_PersonaPlex.docx</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/registers/REG-07_Design_and_Change_Register.md</t>
+          <t>Evidence Library</t>
         </is>
       </c>
     </row>
@@ -1620,22 +1620,22 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>SOP-06 Configuration and change management (significance criteria §6)</t>
+          <t>Review record CR-2026-06 — the client feedback that changed the requirement</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/procedures__SOP-06_Configuration_and_Change_Management.docx</t>
+          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/CR-2026-06_Live_transcription.docx</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>QMS</t>
+          <t>Evidence Library</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>FRM-02 Change request (form)</t>
+          <t>REG-07 Design and change register</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/forms__FRM-02_Change_Request.docx</t>
+          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/registers__REG-07_Design_and_Change_Register.docx</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>QMS forms</t>
+          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/registers/REG-07_Design_and_Change_Register.md</t>
         </is>
       </c>
     </row>
@@ -1684,118 +1684,118 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>EM26-20 › sheet ‘Requirement changes’ RC-2025-01 … RC-2026-07</t>
+          <t>SOP-06 Configuration and change management (significance criteria §6)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/EM26-20_Functional_Requirements.xlsx</t>
+          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/procedures__SOP-06_Configuration_and_Change_Management.docx</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Controlled copy</t>
+          <t>QMS</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>06_Design_and_Development</t>
+          <t>05_Changes_to_Requirements</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Design and development process ECH-QMS-011 (inputs, outputs, controls); hardware BOM</t>
+          <t>FRM-02 Change request (form)</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/forms__FRM-02_Change_Request.docx</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>QMS forms</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>06_Design_and_Development</t>
+          <t>05_Changes_to_Requirements</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Architecture alignment workshop minutes MM-ECHO-2025-05</t>
+          <t>EM26-20 › sheet ‘Requirement changes’ RC-2025-01 … RC-2026-07</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/EM26-20_Functional_Requirements.xlsx</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>Controlled copy</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>06_Design_and_Development</t>
+          <t>05_Changes_to_Requirements</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-04 — design decision</t>
+          <t>EM26-30 Requirement Change Record</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>06_Design_and_Development/2026_EchoMind_Enterprise/CR-2026-04_Conversation_assistance_v2_NVIDIA_PersonaPlex.docx</t>
+          <t>05_Changes_to_Requirements/EM26-30_Requirement_Change_Record.docx</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Evidence Library</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1807,27 +1807,27 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-05 — design decision</t>
+          <t>Design and development process ECH-QMS-011 (inputs, outputs, controls); hardware BOM</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>06_Design_and_Development/2026_EchoMind_Enterprise/CR-2026-05_Field_deployment_of_the_unit.docx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Evidence Library</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -1839,27 +1839,27 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-08 — design decision</t>
+          <t>Architecture alignment workshop minutes MM-ECHO-2025-05</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>06_Design_and_Development/2026_EchoMind_Enterprise/CR-2026-08_Group_discussions_Boardroom.docx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Evidence Library</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Review record SR-2026-01 — design decision</t>
+          <t>Review record CR-2026-04 — design decision</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>06_Design_and_Development/2026_EchoMind_Enterprise/SR-2026-01_Security_and_defect_review_across_RAG_transcriptio.docx</t>
+          <t>06_Design_and_Development/2026_EchoMind_Enterprise/CR-2026-04_Conversation_assistance_v2_NVIDIA_PersonaPlex.docx</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -1908,22 +1908,22 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Design output — capabilities and how each module works</t>
+          <t>Review record CR-2026-05 — design decision</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>06_Design_and_Development/2026_EchoMind_Enterprise/CAPABILITIES.md</t>
+          <t>06_Design_and_Development/2026_EchoMind_Enterprise/CR-2026-05_Field_deployment_of_the_unit.docx</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/CAPABILITIES.md</t>
+          <t>Evidence Library</t>
         </is>
       </c>
     </row>
@@ -1940,22 +1940,22 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Design verification — dual-loop architecture, measured (QASC 2026)</t>
+          <t>Review record CR-2026-08 — design decision</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>06_Design_and_Development/2026_EchoMind_Enterprise/EchoMind_QASC2026_CameraReady_v4.pdf</t>
+          <t>06_Design_and_Development/2026_EchoMind_Enterprise/CR-2026-08_Group_discussions_Boardroom.docx</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/tree/main/docs/paper</t>
+          <t>Evidence Library</t>
         </is>
       </c>
     </row>
@@ -1972,22 +1972,22 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>EM26-11 Deliverables review (Feb–Oct 2026)</t>
+          <t>Review record SR-2026-01 — design decision</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>06_Design_and_Development/2026_EchoMind_Enterprise/EM26-11_Deliverables_Review.docx</t>
+          <t>06_Design_and_Development/2026_EchoMind_Enterprise/SR-2026-01_Security_and_defect_review_across_RAG_transcriptio.docx</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Evidence pack</t>
+          <t>Evidence Library</t>
         </is>
       </c>
     </row>
@@ -2004,150 +2004,150 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>SOP-05 Design and development control</t>
+          <t>Design output — capabilities and how each module works</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>06_Design_and_Development/2026_EchoMind_Enterprise/procedures__SOP-05_Design_and_Development_Control.docx</t>
+          <t>06_Design_and_Development/2026_EchoMind_Enterprise/CAPABILITIES.md</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>QMS</t>
+          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/CAPABILITIES.md</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>07_Review_Records</t>
+          <t>06_Design_and_Development</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>2025 review record / minutes — AJACE Deliverables Review EchoMind</t>
+          <t>Design verification — dual-loop architecture, measured (QASC 2026)</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>06_Design_and_Development/2026_EchoMind_Enterprise/EchoMind_QASC2026_CameraReady_v4.pdf</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>https://github.com/RW2523/echomind-enterprise/tree/main/docs/paper</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>07_Review_Records</t>
+          <t>06_Design_and_Development</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>2025 review record / minutes — AJACE Scheduling Review EchoMind</t>
+          <t>EM26-11 Deliverables review (Feb–Oct 2026)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>06_Design_and_Development/2026_EchoMind_Enterprise/EM26-11_Deliverables_Review.docx</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>Evidence pack</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>07_Review_Records</t>
+          <t>06_Design_and_Development</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>2025 review record / minutes — AJACE Acceptance Criteria Review EchoMind</t>
+          <t>SOP-05 Design and development control</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>06_Design_and_Development/2026_EchoMind_Enterprise/procedures__SOP-05_Design_and_Development_Control.docx</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>QMS</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>07_Review_Records</t>
+          <t>06_Design_and_Development</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>2025 review record / minutes — Meeting Minutes Architecture Workshop EchoMind</t>
+          <t>EM26-31 Design and Development Record</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>06_Design_and_Development/EM26-31_Design_and_Development_Record.docx</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>2025 review record / minutes — Meeting Minutes QA Sprint EchoMind</t>
+          <t>2025 review record / minutes — AJACE Deliverables Review EchoMind</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>2025 review record / minutes — Meeting Minutes Provider Review EchoMind</t>
+          <t>2025 review record / minutes — AJACE Scheduling Review EchoMind</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -2223,27 +2223,27 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 All Review Records</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Review records DR-2025-01 … 15, CR-2026-01 … 09, SR-2026-01, RV-2026-01 … 08 (33)</t>
+          <t>2025 review record / minutes — AJACE Acceptance Criteria Review EchoMind</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>2025-05 → 2026-10</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>07_Review_Records/2025-2026_All_Review_Records/Review_Records_all_33</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Evidence Library</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -2255,27 +2255,27 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>EM26-18 Review feedback and action log (2025 finding #7)</t>
+          <t>2025 review record / minutes — Meeting Minutes Architecture Workshop EchoMind</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>07_Review_Records/2026_EchoMind_Enterprise/EM26-18_Deliverable_Review_Feedback_and_Action_Log.docx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Controlled copy</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -2287,34 +2287,34 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>EM26-19 Review feedback and action log (review cycle, version reviews, 75 actions)</t>
+          <t>2025 review record / minutes — Meeting Minutes QA Sprint EchoMind</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>07_Review_Records/2026_EchoMind_Enterprise/EM26-19_Deliverable_Review_Feedback_and_Action_Log.xlsx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Controlled copy</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>08_Test_Plan_and_Test_Cases</t>
+          <t>07_Review_Records</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>2025 test case TC-EM-UI-Upload-001</t>
+          <t>2025 review record / minutes — Meeting Minutes Provider Review EchoMind</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -2346,71 +2346,71 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>08_Test_Plan_and_Test_Cases</t>
+          <t>07_Review_Records</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2025-2026 All Review Records</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>2025 test case TC-EM-Stacks-002</t>
+          <t>Review records DR-2025-01 … 15, CR-2026-01 … 09, SR-2026-01, RV-2026-01 … 08 (33)</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025-05 → 2026-10</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>07_Review_Records/2025-2026_All_Review_Records/Review_Records_all_33</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>Evidence Library</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>08_Test_Plan_and_Test_Cases</t>
+          <t>07_Review_Records</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>2025 test case TC-EM-Transcribe-003</t>
+          <t>EM26-18 Review feedback and action log (2025 finding #7)</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>07_Review_Records/2026_EchoMind_Enterprise/EM26-18_Deliverable_Review_Feedback_and_Action_Log.docx</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>Controlled copy</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>08_Test_Plan_and_Test_Cases</t>
+          <t>07_Review_Records</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -2420,22 +2420,22 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>EM26-13 Acceptance criteria review</t>
+          <t>EM26-19 Review feedback and action log (review cycle, version reviews, 75 actions)</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/EM26-13_Acceptance_Criteria_Review.docx</t>
+          <t>07_Review_Records/2026_EchoMind_Enterprise/EM26-19_Deliverable_Review_Feedback_and_Action_Log.xlsx</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Evidence pack</t>
+          <t>Controlled copy</t>
         </is>
       </c>
     </row>
@@ -2447,27 +2447,27 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>13 acceptance test cases TC-EM-AUTH-101 … TC-EM-EVAL-114</t>
+          <t>2025 test case TC-EM-UI-Upload-001</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/Test_Cases</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Evidence pack</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -2479,27 +2479,27 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>SOP-07 Verification, validation and testing</t>
+          <t>2025 test case TC-EM-Stacks-002</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/procedures__SOP-07_Verification_Validation_and_Testing.docx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>QMS</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -2511,155 +2511,155 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>EM26-24 Test Plan — EchoMind Enterprise</t>
+          <t>2025 test case TC-EM-Transcribe-003</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/EM26-24_Test_Plan_EchoMind_Enterprise.docx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>09_Test_Reports</t>
+          <t>08_Test_Plan_and_Test_Cases</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2025 test report — Failed Functional Test QA-FAIL-01</t>
+          <t>EM26-13 Acceptance criteria review</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/EM26-13_Acceptance_Criteria_Review.docx</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>Evidence pack</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>09_Test_Reports</t>
+          <t>08_Test_Plan_and_Test_Cases</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>2025 test report — Defect Linking Jira DEF-2025-01</t>
+          <t>13 acceptance test cases TC-EM-AUTH-101 … TC-EM-EVAL-114</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/Test_Cases</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>Evidence pack</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>09_Test_Reports</t>
+          <t>08_Test_Plan_and_Test_Cases</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>2025 test report — Regression Testing Defects REG-2025-01</t>
+          <t>SOP-07 Verification, validation and testing</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/procedures__SOP-07_Verification_Validation_and_Testing.docx</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>QMS</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>09_Test_Reports</t>
+          <t>08_Test_Plan_and_Test_Cases</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>2025 test report — AJACE Test Failure EchoMind</t>
+          <t>EM26-24 Test Plan — EchoMind Enterprise</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/EM26-24_Test_Plan_EchoMind_Enterprise.docx</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -2671,27 +2671,27 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Golden-question evaluation runs (24, 2026-07-29 → 09-22)</t>
+          <t>2025 test report — Failed Functional Test QA-FAIL-01</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29 → 09-22</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>09_Test_Reports/2026_EchoMind_Enterprise/Golden_Suite_Runs</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/tree/main/eval/reports</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -2703,27 +2703,27 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>EM26-15 Test summary report</t>
+          <t>2025 test report — Defect Linking Jira DEF-2025-01</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>09_Test_Reports/2026_EchoMind_Enterprise/EM26-15_Test_Summary_Report.docx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Evidence pack</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -2735,27 +2735,27 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Acceptance test execution runs 1–4 (2026-10-06)</t>
+          <t>2025 test report — Regression Testing Defects REG-2025-01</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>09_Test_Reports/2026_EchoMind_Enterprise/Execution_Records_run1-4</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Evidence pack</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -2767,27 +2767,27 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Failure → defect → regression records QA-FAIL-2026-01 … 07, DEF-2026-01, REG-2026-01</t>
+          <t>2025 test report — AJACE Test Failure EchoMind</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>09_Test_Reports/2026_EchoMind_Enterprise/Failure_Defect_Regression</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Evidence pack</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -2804,61 +2804,61 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>CI runs and tickets</t>
+          <t>Golden-question evaluation runs (24, 2026-07-29 → 09-22)</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-07-29 → 09-22</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>09_Test_Reports/2026_EchoMind_Enterprise/CI_Runs_and_Tickets</t>
+          <t>09_Test_Reports/2026_EchoMind_Enterprise/Golden_Suite_Runs</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>https://github.com/RW2523/echomind-enterprise/tree/main/eval/reports</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>10_Identification_and_Traceability</t>
+          <t>09_Test_Reports</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Appliance identification ‘EchoMind – university’ unit; UPS tracking; versioned Git</t>
+          <t>EM26-15 Test summary report</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>09_Test_Reports/2026_EchoMind_Enterprise/EM26-15_Test_Summary_Report.docx</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>Evidence pack</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>10_Identification_and_Traceability</t>
+          <t>09_Test_Reports</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>TC-EM-REL-106 Release identification test (pass, run 4)</t>
+          <t>Acceptance test execution runs 1–4 (2026-10-06)</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/TC-EM-REL-106_Release_identification_and_traceability.docx</t>
+          <t>09_Test_Reports/2026_EchoMind_Enterprise/Execution_Records_run1-4</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -2890,7 +2890,7 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>10_Identification_and_Traceability</t>
+          <t>09_Test_Reports</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -2900,29 +2900,29 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>REG-08 Release and deployment register (versions v1.0.0 → v1.4.1, deployments)</t>
+          <t>Failure → defect → regression records QA-FAIL-2026-01 … 07, DEF-2026-01, REG-2026-01</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/registers__REG-08_Release_and_Deployment_Register.docx</t>
+          <t>09_Test_Reports/2026_EchoMind_Enterprise/Failure_Defect_Regression</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/registers/REG-08_Release_and_Deployment_Register.md</t>
+          <t>Evidence pack</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>10_Identification_and_Traceability</t>
+          <t>09_Test_Reports</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -2932,22 +2932,22 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Version tags v1.0.0 → v1.4.1 with their messages</t>
+          <t>CI runs and tickets</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/version_tags.txt</t>
+          <t>09_Test_Reports/2026_EchoMind_Enterprise/CI_Runs_and_Tickets</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/tags</t>
+          <t>GitHub</t>
         </is>
       </c>
     </row>
@@ -2959,66 +2959,66 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>EM26-20 › sheet ‘Traceability’ (requirement → review → commit → version → test → release)</t>
+          <t>Appliance identification ‘EchoMind – university’ unit; UPS tracking; versioned Git</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/EM26-20_Functional_Requirements.xlsx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Controlled copy</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>11_Release_Notes</t>
+          <t>10_Identification_and_Traceability</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Final release package approved and released (MM-2025-09-01)</t>
+          <t>TC-EM-REL-106 Release identification test (pass, run 4)</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/TC-EM-REL-106_Release_identification_and_traceability.docx</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>Evidence pack</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>11_Release_Notes</t>
+          <t>10_Identification_and_Traceability</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -3028,29 +3028,29 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Release record (FRM-03) v1.4.0</t>
+          <t>REG-08 Release and deployment register (versions v1.0.0 → v1.4.1, deployments)</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>11_Release_Notes/2026_EchoMind_Enterprise/records__releases__2026-10-06_v1.4.0.docx</t>
+          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/registers__REG-08_Release_and_Deployment_Register.docx</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/records/releases/2026-10-06_v1.4.0.md</t>
+          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/registers/REG-08_Release_and_Deployment_Register.md</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>11_Release_Notes</t>
+          <t>10_Identification_and_Traceability</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -3060,29 +3060,29 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Release record (FRM-03) v1.4.1</t>
+          <t>Version tags v1.0.0 → v1.4.1 with their messages</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>11_Release_Notes/2026_EchoMind_Enterprise/records__releases__2026-10-06_v1.4.1.docx</t>
+          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/version_tags.txt</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/records/releases/2026-10-06_v1.4.1.md</t>
+          <t>https://github.com/RW2523/echomind-enterprise/tags</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>11_Release_Notes</t>
+          <t>10_Identification_and_Traceability</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>CHANGELOG — one section per version</t>
+          <t>EM26-20 › sheet ‘Traceability’ (requirement → review → commit → version → test → release)</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -3102,39 +3102,39 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>11_Release_Notes/2026_EchoMind_Enterprise/CHANGELOG.md</t>
+          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/EM26-20_Functional_Requirements.xlsx</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/blob/main/CHANGELOG.md</t>
+          <t>Controlled copy</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>11_Release_Notes</t>
+          <t>10_Identification_and_Traceability</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>EM26-25 Release Notes v1.0.0 → v1.4.1</t>
+          <t>EM26-32 Identification and Traceability Record</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>11_Release_Notes/2026_EchoMind_Enterprise/EM26-25_Release_Notes_v1.0.0-v1.4.1.docx</t>
+          <t>10_Identification_and_Traceability/EM26-32_Identification_and_Traceability_Record.docx</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -3146,7 +3146,7 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>12_Lessons_Learnt</t>
+          <t>11_Release_Notes</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>2025 lessons learnt — AJACE EchoMind Lessons Learned Log (May–Sep 2025)</t>
+          <t>Final release package approved and released (MM-2025-09-01)</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -3178,71 +3178,71 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>12_Lessons_Learnt</t>
+          <t>11_Release_Notes</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>2025 lessons learnt — 16. AJACE_Lessons_Learnt_EchoMind</t>
+          <t>Release record (FRM-03) v1.4.0</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>11_Release_Notes/2026_EchoMind_Enterprise/records__releases__2026-10-06_v1.4.0.docx</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/records/releases/2026-10-06_v1.4.0.md</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>12_Lessons_Learnt</t>
+          <t>11_Release_Notes</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>2025 lessons learnt — 16b. AJACE_Lessons_Learnt_Logbook_EchoMind</t>
+          <t>Release record (FRM-03) v1.4.1</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>11_Release_Notes/2026_EchoMind_Enterprise/records__releases__2026-10-06_v1.4.1.docx</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/records/releases/2026-10-06_v1.4.1.md</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>12_Lessons_Learnt</t>
+          <t>11_Release_Notes</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -3252,29 +3252,29 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>2026 lessons learnt — EM26-16 Lessons Learnt</t>
+          <t>CHANGELOG — one section per version</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>12_Lessons_Learnt/2026_EchoMind_Enterprise/EM26-16_Lessons_Learnt.docx</t>
+          <t>11_Release_Notes/2026_EchoMind_Enterprise/CHANGELOG.md</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Evidence pack</t>
+          <t>https://github.com/RW2523/echomind-enterprise/blob/main/CHANGELOG.md</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>12_Lessons_Learnt</t>
+          <t>11_Release_Notes</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -3284,22 +3284,22 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>2026 lessons learnt — EM26-16b Lessons Learnt Logbook</t>
+          <t>EM26-25 Release Notes v1.0.0 → v1.4.1</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>12_Lessons_Learnt/2026_EchoMind_Enterprise/EM26-16b_Lessons_Learnt_Logbook.docx</t>
+          <t>11_Release_Notes/2026_EchoMind_Enterprise/EM26-25_Release_Notes_v1.0.0-v1.4.1.docx</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Evidence pack</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -3311,128 +3311,288 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>2026 lessons learnt — EM26-16 Lessons Learnt Log</t>
+          <t>2025 lessons learnt — AJACE EchoMind Lessons Learned Log (May–Sep 2025)</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>12_Lessons_Learnt/2026_EchoMind_Enterprise/EM26-16_Lessons_Learnt_Log.xlsx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Evidence pack</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>13_New_Use_Case_EchoMind</t>
+          <t>12_Lessons_Learnt</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Capabilities of the five modules</t>
+          <t>2025 lessons learnt — 16. AJACE_Lessons_Learnt_EchoMind</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>13_New_Use_Case_EchoMind/2026_EchoMind_Enterprise/CAPABILITIES.md</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>docs</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>13_New_Use_Case_EchoMind</t>
+          <t>12_Lessons_Learnt</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>QASC 2026 paper — EchoMind architecture and results</t>
+          <t>2025 lessons learnt — 16b. AJACE_Lessons_Learnt_Logbook_EchoMind</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>13_New_Use_Case_EchoMind/2026_EchoMind_Enterprise/EchoMind_QASC2026_CameraReady_v4.pdf</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>docs/paper</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
+          <t>12_Lessons_Learnt</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>2026 EchoMind Enterprise</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>2026 lessons learnt — EM26-16 Lessons Learnt</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>12_Lessons_Learnt/2026_EchoMind_Enterprise/EM26-16_Lessons_Learnt.docx</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>Evidence pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>12_Lessons_Learnt</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>2026 EchoMind Enterprise</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>2026 lessons learnt — EM26-16b Lessons Learnt Logbook</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>12_Lessons_Learnt/2026_EchoMind_Enterprise/EM26-16b_Lessons_Learnt_Logbook.docx</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>Evidence pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>12_Lessons_Learnt</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>2026 EchoMind Enterprise</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>2026 lessons learnt — EM26-16 Lessons Learnt Log</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>12_Lessons_Learnt/2026_EchoMind_Enterprise/EM26-16_Lessons_Learnt_Log.xlsx</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>Evidence pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
           <t>13_New_Use_Case_EchoMind</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>2026 EchoMind Enterprise</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>2026 EchoMind Enterprise</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>Capabilities of the five modules</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>13_New_Use_Case_EchoMind/2026_EchoMind_Enterprise/CAPABILITIES.md</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>13_New_Use_Case_EchoMind</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>2026 EchoMind Enterprise</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>QASC 2026 paper — EchoMind architecture and results</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>13_New_Use_Case_EchoMind/2026_EchoMind_Enterprise/EchoMind_QASC2026_CameraReady_v4.pdf</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>docs/paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>13_New_Use_Case_EchoMind</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>2026 EchoMind Enterprise</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
         <is>
           <t>EM26-26 New Use Cases — EchoMind Enterprise</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
+      <c r="D100" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
+      <c r="E100" s="4" t="inlineStr">
         <is>
           <t>13_New_Use_Case_EchoMind/2026_EchoMind_Enterprise/EM26-26_New_Use_Cases_EchoMind_Enterprise.docx</t>
         </is>
       </c>
-      <c r="F95" s="4" t="inlineStr">
+      <c r="F100" s="4" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F95"/>
+  <autoFilter ref="A4:F100"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/EchoMind_Audit_2026-10-14_Project2/00_Evidence_Index.xlsx
+++ b/docs/EchoMind_Audit_2026-10-14_Project2/00_Evidence_Index.xlsx
@@ -724,7 +724,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>EM26-28 Contract Review Record</t>
+          <t>EM26-28 Development Side Contract Review</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>01_Contract_Review/EM26-28_Contract_Review_Record.docx</t>
+          <t>01_Contract_Review/EM26-28_Development_Side_Contract_Review.docx</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">

--- a/docs/EchoMind_Audit_2026-10-14_Project2/00_Evidence_Index.xlsx
+++ b/docs/EchoMind_Audit_2026-10-14_Project2/00_Evidence_Index.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retrieve before the session" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evidence index'!$A$4:$F$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evidence index'!$A$4:$F$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Retrieve before the session'!$A$4:$C$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1322,32 +1322,32 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>04_Requirements</t>
+          <t>03_Communication_with_Client</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Requirements (ECH-QMS-010): fully offline on-premises AI system; BYOA pilot; acceptance by end-to-end test</t>
+          <t>EM26-27 Client Communication Record (rev 1.1)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>03_Communication_with_Client/EM26-27_Client_Communication_Record.docx</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Acceptance criteria review ACC-1.0</t>
+          <t>Requirements (ECH-QMS-010): fully offline on-premises AI system; BYOA pilot; acceptance by end-to-end test</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1391,27 +1391,27 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>EM26-17 NFR record and monitoring (2025 finding #6)</t>
+          <t>Acceptance criteria review ACC-1.0</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>04_Requirements/2026_EchoMind_Enterprise/EM26-17_NFR_Record_and_Monitoring.docx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Controlled copy</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -1428,17 +1428,17 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>EM26-20 Functional requirements (39) with traceability</t>
+          <t>EM26-17 NFR record and monitoring (2025 finding #6)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>04_Requirements/2026_EchoMind_Enterprise/EM26-20_Functional_Requirements.xlsx</t>
+          <t>04_Requirements/2026_EchoMind_Enterprise/EM26-17_NFR_Record_and_Monitoring.docx</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>EM26-21 Non-functional requirements (31 + 9 from 2025) with measurements</t>
+          <t>EM26-20 Functional requirements (39) with traceability</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>04_Requirements/2026_EchoMind_Enterprise/EM26-21_Non_Functional_Requirements.xlsx</t>
+          <t>04_Requirements/2026_EchoMind_Enterprise/EM26-20_Functional_Requirements.xlsx</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1492,54 +1492,54 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>EM26-29 Software Requirements Specification</t>
+          <t>EM26-21 Non-functional requirements (31 + 9 from 2025) with measurements</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>04_Requirements/EM26-29_Software_Requirements_Specification.docx</t>
+          <t>04_Requirements/2026_EchoMind_Enterprise/EM26-21_Non_Functional_Requirements.xlsx</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Controlled copy</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>05_Changes_to_Requirements</t>
+          <t>04_Requirements</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>2025 change requests CR-2025-01 … 04 (lessons log)</t>
+          <t>EM26-29 Software Requirements Specification</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2025-05 → 09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>04_Requirements/EM26-29_Software_Requirements_Specification.docx</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1551,27 +1551,27 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-03 — the client feedback that changed the requirement</t>
+          <t>2025 change requests CR-2025-01 … 04 (lessons log)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025-05 → 09</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/CR-2026-03_Conversation_assistance_v1_Kyutai_Unmute_stack.docx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Evidence Library</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-04 — the client feedback that changed the requirement</t>
+          <t>Review record CR-2026-03 — the client feedback that changed the requirement</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/CR-2026-04_Conversation_assistance_v2_NVIDIA_PersonaPlex.docx</t>
+          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/CR-2026-03_Conversation_assistance_v1_Kyutai_Unmute_stack.docx</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-06 — the client feedback that changed the requirement</t>
+          <t>Review record CR-2026-04 — the client feedback that changed the requirement</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/CR-2026-06_Live_transcription.docx</t>
+          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/CR-2026-04_Conversation_assistance_v2_NVIDIA_PersonaPlex.docx</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -1652,22 +1652,22 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>REG-07 Design and change register</t>
+          <t>Review record CR-2026-06 — the client feedback that changed the requirement</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/registers__REG-07_Design_and_Change_Register.docx</t>
+          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/CR-2026-06_Live_transcription.docx</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/registers/REG-07_Design_and_Change_Register.md</t>
+          <t>Evidence Library</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>SOP-06 Configuration and change management (significance criteria §6)</t>
+          <t>REG-07 Design and change register</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/procedures__SOP-06_Configuration_and_Change_Management.docx</t>
+          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/registers__REG-07_Design_and_Change_Register.docx</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>QMS</t>
+          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/registers/REG-07_Design_and_Change_Register.md</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>FRM-02 Change request (form)</t>
+          <t>SOP-06 Configuration and change management (significance criteria §6)</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/forms__FRM-02_Change_Request.docx</t>
+          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/procedures__SOP-06_Configuration_and_Change_Management.docx</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>QMS forms</t>
+          <t>QMS</t>
         </is>
       </c>
     </row>
@@ -1748,22 +1748,22 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>EM26-20 › sheet ‘Requirement changes’ RC-2025-01 … RC-2026-07</t>
+          <t>FRM-02 Change request (form)</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/EM26-20_Functional_Requirements.xlsx</t>
+          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/forms__FRM-02_Change_Request.docx</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Controlled copy</t>
+          <t>QMS forms</t>
         </is>
       </c>
     </row>
@@ -1775,59 +1775,59 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>EM26-30 Requirement Change Record</t>
+          <t>EM26-20 › sheet ‘Requirement changes’ RC-2025-01 … RC-2026-07</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>05_Changes_to_Requirements/EM26-30_Requirement_Change_Record.docx</t>
+          <t>05_Changes_to_Requirements/2026_EchoMind_Enterprise/EM26-20_Functional_Requirements.xlsx</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Controlled copy</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>06_Design_and_Development</t>
+          <t>05_Changes_to_Requirements</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Design and development process ECH-QMS-011 (inputs, outputs, controls); hardware BOM</t>
+          <t>EM26-30 Requirement Change Record</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>05_Changes_to_Requirements/EM26-30_Requirement_Change_Record.docx</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Architecture alignment workshop minutes MM-ECHO-2025-05</t>
+          <t>Design and development process ECH-QMS-011 (inputs, outputs, controls); hardware BOM</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -1871,27 +1871,27 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-04 — design decision</t>
+          <t>Architecture alignment workshop minutes MM-ECHO-2025-05</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>06_Design_and_Development/2026_EchoMind_Enterprise/CR-2026-04_Conversation_assistance_v2_NVIDIA_PersonaPlex.docx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Evidence Library</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-05 — design decision</t>
+          <t>Review record CR-2026-04 — design decision</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>06_Design_and_Development/2026_EchoMind_Enterprise/CR-2026-05_Field_deployment_of_the_unit.docx</t>
+          <t>06_Design_and_Development/2026_EchoMind_Enterprise/CR-2026-04_Conversation_assistance_v2_NVIDIA_PersonaPlex.docx</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-08 — design decision</t>
+          <t>Review record CR-2026-05 — design decision</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>06_Design_and_Development/2026_EchoMind_Enterprise/CR-2026-08_Group_discussions_Boardroom.docx</t>
+          <t>06_Design_and_Development/2026_EchoMind_Enterprise/CR-2026-05_Field_deployment_of_the_unit.docx</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Review record SR-2026-01 — design decision</t>
+          <t>Review record CR-2026-08 — design decision</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>06_Design_and_Development/2026_EchoMind_Enterprise/SR-2026-01_Security_and_defect_review_across_RAG_transcriptio.docx</t>
+          <t>06_Design_and_Development/2026_EchoMind_Enterprise/CR-2026-08_Group_discussions_Boardroom.docx</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -2004,22 +2004,22 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Design output — capabilities and how each module works</t>
+          <t>Review record SR-2026-01 — design decision</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>06_Design_and_Development/2026_EchoMind_Enterprise/CAPABILITIES.md</t>
+          <t>06_Design_and_Development/2026_EchoMind_Enterprise/SR-2026-01_Security_and_defect_review_across_RAG_transcriptio.docx</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/CAPABILITIES.md</t>
+          <t>Evidence Library</t>
         </is>
       </c>
     </row>
@@ -2036,22 +2036,22 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Design verification — dual-loop architecture, measured (QASC 2026)</t>
+          <t>Design output — capabilities and how each module works</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>06_Design_and_Development/2026_EchoMind_Enterprise/EchoMind_QASC2026_CameraReady_v4.pdf</t>
+          <t>06_Design_and_Development/2026_EchoMind_Enterprise/CAPABILITIES.md</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/tree/main/docs/paper</t>
+          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/CAPABILITIES.md</t>
         </is>
       </c>
     </row>
@@ -2068,22 +2068,22 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>EM26-11 Deliverables review (Feb–Oct 2026)</t>
+          <t>Design verification — dual-loop architecture, measured (QASC 2026)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>06_Design_and_Development/2026_EchoMind_Enterprise/EM26-11_Deliverables_Review.docx</t>
+          <t>06_Design_and_Development/2026_EchoMind_Enterprise/EchoMind_QASC2026_CameraReady_v4.pdf</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Evidence pack</t>
+          <t>https://github.com/RW2523/echomind-enterprise/tree/main/docs/paper</t>
         </is>
       </c>
     </row>
@@ -2100,22 +2100,22 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>SOP-05 Design and development control</t>
+          <t>EM26-11 Deliverables review (Feb–Oct 2026)</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>06_Design_and_Development/2026_EchoMind_Enterprise/procedures__SOP-05_Design_and_Development_Control.docx</t>
+          <t>06_Design_and_Development/2026_EchoMind_Enterprise/EM26-11_Deliverables_Review.docx</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>QMS</t>
+          <t>Evidence pack</t>
         </is>
       </c>
     </row>
@@ -2127,59 +2127,59 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>EM26-31 Design and Development Record</t>
+          <t>SOP-05 Design and development control</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>06_Design_and_Development/EM26-31_Design_and_Development_Record.docx</t>
+          <t>06_Design_and_Development/2026_EchoMind_Enterprise/procedures__SOP-05_Design_and_Development_Control.docx</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>QMS</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>07_Review_Records</t>
+          <t>06_Design_and_Development</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>2025 review record / minutes — AJACE Deliverables Review EchoMind</t>
+          <t>EM26-31 Design and Development Record</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>06_Design_and_Development/EM26-31_Design_and_Development_Record.docx</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>2025 review record / minutes — AJACE Scheduling Review EchoMind</t>
+          <t>2025 review record / minutes — AJACE Deliverables Review EchoMind</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>2025 review record / minutes — AJACE Acceptance Criteria Review EchoMind</t>
+          <t>2025 review record / minutes — AJACE Scheduling Review EchoMind</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>2025 review record / minutes — Meeting Minutes Architecture Workshop EchoMind</t>
+          <t>2025 review record / minutes — AJACE Acceptance Criteria Review EchoMind</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>2025 review record / minutes — Meeting Minutes QA Sprint EchoMind</t>
+          <t>2025 review record / minutes — Meeting Minutes Architecture Workshop EchoMind</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>2025 review record / minutes — Meeting Minutes Provider Review EchoMind</t>
+          <t>2025 review record / minutes — Meeting Minutes QA Sprint EchoMind</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -2351,27 +2351,27 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 All Review Records</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Review records DR-2025-01 … 15, CR-2026-01 … 09, SR-2026-01, RV-2026-01 … 08 (33)</t>
+          <t>2025 review record / minutes — Meeting Minutes Provider Review EchoMind</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>2025-05 → 2026-10</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>07_Review_Records/2025-2026_All_Review_Records/Review_Records_all_33</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Evidence Library</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -2383,27 +2383,27 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025-2026 All Review Records</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>EM26-18 Review feedback and action log (2025 finding #7)</t>
+          <t>Review records DR-2025-01 … 15, CR-2026-01 … 09, SR-2026-01, RV-2026-01 … 08 (33)</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2025-05 → 2026-10</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>07_Review_Records/2026_EchoMind_Enterprise/EM26-18_Deliverable_Review_Feedback_and_Action_Log.docx</t>
+          <t>07_Review_Records/2025-2026_All_Review_Records/Review_Records_all_33</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Controlled copy</t>
+          <t>Evidence Library</t>
         </is>
       </c>
     </row>
@@ -2420,17 +2420,17 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>EM26-19 Review feedback and action log (review cycle, version reviews, 75 actions)</t>
+          <t>EM26-18 Review feedback and action log (2025 finding #7)</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>07_Review_Records/2026_EchoMind_Enterprise/EM26-19_Deliverable_Review_Feedback_and_Action_Log.xlsx</t>
+          <t>07_Review_Records/2026_EchoMind_Enterprise/EM26-18_Deliverable_Review_Feedback_and_Action_Log.docx</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -2442,32 +2442,32 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>08_Test_Plan_and_Test_Cases</t>
+          <t>07_Review_Records</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>2025 test case TC-EM-UI-Upload-001</t>
+          <t>EM26-19 Review feedback and action log (review cycle, version reviews, 75 actions)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>07_Review_Records/2026_EchoMind_Enterprise/EM26-19_Deliverable_Review_Feedback_and_Action_Log.xlsx</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>Controlled copy</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>2025 test case TC-EM-Stacks-002</t>
+          <t>2025 test case TC-EM-UI-Upload-001</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>2025 test case TC-EM-Transcribe-003</t>
+          <t>2025 test case TC-EM-Stacks-002</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -2543,27 +2543,27 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>EM26-13 Acceptance criteria review</t>
+          <t>2025 test case TC-EM-Transcribe-003</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/EM26-13_Acceptance_Criteria_Review.docx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Evidence pack</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>13 acceptance test cases TC-EM-AUTH-101 … TC-EM-EVAL-114</t>
+          <t>EM26-13 Acceptance criteria review</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/Test_Cases</t>
+          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/EM26-13_Acceptance_Criteria_Review.docx</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>SOP-07 Verification, validation and testing</t>
+          <t>13 acceptance test cases TC-EM-AUTH-101 … TC-EM-EVAL-114</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/procedures__SOP-07_Verification_Validation_and_Testing.docx</t>
+          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/Test_Cases</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>QMS</t>
+          <t>Evidence pack</t>
         </is>
       </c>
     </row>
@@ -2644,54 +2644,54 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>EM26-24 Test Plan — EchoMind Enterprise</t>
+          <t>SOP-07 Verification, validation and testing</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/EM26-24_Test_Plan_EchoMind_Enterprise.docx</t>
+          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/procedures__SOP-07_Verification_Validation_and_Testing.docx</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>QMS</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>09_Test_Reports</t>
+          <t>08_Test_Plan_and_Test_Cases</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>2025 test report — Failed Functional Test QA-FAIL-01</t>
+          <t>EM26-24 Test Plan — EchoMind Enterprise</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/EM26-24_Test_Plan_EchoMind_Enterprise.docx</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>2025 test report — Defect Linking Jira DEF-2025-01</t>
+          <t>2025 test report — Failed Functional Test QA-FAIL-01</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>2025 test report — Regression Testing Defects REG-2025-01</t>
+          <t>2025 test report — Defect Linking Jira DEF-2025-01</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>2025 test report — AJACE Test Failure EchoMind</t>
+          <t>2025 test report — Regression Testing Defects REG-2025-01</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -2799,27 +2799,27 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Golden-question evaluation runs (24, 2026-07-29 → 09-22)</t>
+          <t>2025 test report — AJACE Test Failure EchoMind</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29 → 09-22</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>09_Test_Reports/2026_EchoMind_Enterprise/Golden_Suite_Runs</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/tree/main/eval/reports</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -2836,22 +2836,22 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>EM26-15 Test summary report</t>
+          <t>Golden-question evaluation runs (24, 2026-07-29 → 09-22)</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-07-29 → 09-22</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>09_Test_Reports/2026_EchoMind_Enterprise/EM26-15_Test_Summary_Report.docx</t>
+          <t>09_Test_Reports/2026_EchoMind_Enterprise/Golden_Suite_Runs</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Evidence pack</t>
+          <t>https://github.com/RW2523/echomind-enterprise/tree/main/eval/reports</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Acceptance test execution runs 1–4 (2026-10-06)</t>
+          <t>EM26-15 Test summary report</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>09_Test_Reports/2026_EchoMind_Enterprise/Execution_Records_run1-4</t>
+          <t>09_Test_Reports/2026_EchoMind_Enterprise/EM26-15_Test_Summary_Report.docx</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Failure → defect → regression records QA-FAIL-2026-01 … 07, DEF-2026-01, REG-2026-01</t>
+          <t>Acceptance test execution runs 1–4 (2026-10-06)</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>09_Test_Reports/2026_EchoMind_Enterprise/Failure_Defect_Regression</t>
+          <t>09_Test_Reports/2026_EchoMind_Enterprise/Execution_Records_run1-4</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -2932,54 +2932,54 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>CI runs and tickets</t>
+          <t>Failure → defect → regression records QA-FAIL-2026-01 … 07, DEF-2026-01, REG-2026-01</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>09_Test_Reports/2026_EchoMind_Enterprise/CI_Runs_and_Tickets</t>
+          <t>09_Test_Reports/2026_EchoMind_Enterprise/Failure_Defect_Regression</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>Evidence pack</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>10_Identification_and_Traceability</t>
+          <t>09_Test_Reports</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Appliance identification ‘EchoMind – university’ unit; UPS tracking; versioned Git</t>
+          <t>CI runs and tickets</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>09_Test_Reports/2026_EchoMind_Enterprise/CI_Runs_and_Tickets</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>GitHub</t>
         </is>
       </c>
     </row>
@@ -2991,27 +2991,27 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>TC-EM-REL-106 Release identification test (pass, run 4)</t>
+          <t>Appliance identification ‘EchoMind – university’ unit; UPS tracking; versioned Git</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/TC-EM-REL-106_Release_identification_and_traceability.docx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Evidence pack</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -3028,22 +3028,22 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>REG-08 Release and deployment register (versions v1.0.0 → v1.4.1, deployments)</t>
+          <t>TC-EM-REL-106 Release identification test (pass, run 4)</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/registers__REG-08_Release_and_Deployment_Register.docx</t>
+          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/TC-EM-REL-106_Release_identification_and_traceability.docx</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/registers/REG-08_Release_and_Deployment_Register.md</t>
+          <t>Evidence pack</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Version tags v1.0.0 → v1.4.1 with their messages</t>
+          <t>REG-08 Release and deployment register (versions v1.0.0 → v1.4.1, deployments)</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/version_tags.txt</t>
+          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/registers__REG-08_Release_and_Deployment_Register.docx</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/tags</t>
+          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/registers/REG-08_Release_and_Deployment_Register.md</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>EM26-20 › sheet ‘Traceability’ (requirement → review → commit → version → test → release)</t>
+          <t>Version tags v1.0.0 → v1.4.1 with their messages</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -3102,12 +3102,12 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/EM26-20_Functional_Requirements.xlsx</t>
+          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/version_tags.txt</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Controlled copy</t>
+          <t>https://github.com/RW2523/echomind-enterprise/tags</t>
         </is>
       </c>
     </row>
@@ -3119,59 +3119,59 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>EM26-32 Identification and Traceability Record</t>
+          <t>EM26-20 › sheet ‘Traceability’ (requirement → review → commit → version → test → release)</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>10_Identification_and_Traceability/EM26-32_Identification_and_Traceability_Record.docx</t>
+          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/EM26-20_Functional_Requirements.xlsx</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Controlled copy</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>11_Release_Notes</t>
+          <t>10_Identification_and_Traceability</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Final release package approved and released (MM-2025-09-01)</t>
+          <t>EM26-32 Identification and Traceability Record</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>10_Identification_and_Traceability/EM26-32_Identification_and_Traceability_Record.docx</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -3183,27 +3183,27 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Release record (FRM-03) v1.4.0</t>
+          <t>Final release package approved and released (MM-2025-09-01)</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>11_Release_Notes/2026_EchoMind_Enterprise/records__releases__2026-10-06_v1.4.0.docx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/records/releases/2026-10-06_v1.4.0.md</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Release record (FRM-03) v1.4.1</t>
+          <t>Release record (FRM-03) v1.4.0</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>11_Release_Notes/2026_EchoMind_Enterprise/records__releases__2026-10-06_v1.4.1.docx</t>
+          <t>11_Release_Notes/2026_EchoMind_Enterprise/records__releases__2026-10-06_v1.4.0.docx</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/records/releases/2026-10-06_v1.4.1.md</t>
+          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/records/releases/2026-10-06_v1.4.0.md</t>
         </is>
       </c>
     </row>
@@ -3252,22 +3252,22 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>CHANGELOG — one section per version</t>
+          <t>Release record (FRM-03) v1.4.1</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>11_Release_Notes/2026_EchoMind_Enterprise/CHANGELOG.md</t>
+          <t>11_Release_Notes/2026_EchoMind_Enterprise/records__releases__2026-10-06_v1.4.1.docx</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/blob/main/CHANGELOG.md</t>
+          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/records/releases/2026-10-06_v1.4.1.md</t>
         </is>
       </c>
     </row>
@@ -3284,54 +3284,54 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>EM26-25 Release Notes v1.0.0 → v1.4.1</t>
+          <t>CHANGELOG — one section per version</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>11_Release_Notes/2026_EchoMind_Enterprise/EM26-25_Release_Notes_v1.0.0-v1.4.1.docx</t>
+          <t>11_Release_Notes/2026_EchoMind_Enterprise/CHANGELOG.md</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>https://github.com/RW2523/echomind-enterprise/blob/main/CHANGELOG.md</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>12_Lessons_Learnt</t>
+          <t>11_Release_Notes</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>2025 lessons learnt — AJACE EchoMind Lessons Learned Log (May–Sep 2025)</t>
+          <t>EM26-25 Release Notes v1.0.0 → v1.4.1</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>11_Release_Notes/2026_EchoMind_Enterprise/EM26-25_Release_Notes_v1.0.0-v1.4.1.docx</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>2025 lessons learnt — 16. AJACE_Lessons_Learnt_EchoMind</t>
+          <t>2025 lessons learnt — AJACE EchoMind Lessons Learned Log (May–Sep 2025)</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>2025 lessons learnt — 16b. AJACE_Lessons_Learnt_Logbook_EchoMind</t>
+          <t>2025 lessons learnt — 16. AJACE_Lessons_Learnt_EchoMind</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -3407,27 +3407,27 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>2026 lessons learnt — EM26-16 Lessons Learnt</t>
+          <t>2025 lessons learnt — 16b. AJACE_Lessons_Learnt_Logbook_EchoMind</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>12_Lessons_Learnt/2026_EchoMind_Enterprise/EM26-16_Lessons_Learnt.docx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Evidence pack</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>2026 lessons learnt — EM26-16b Lessons Learnt Logbook</t>
+          <t>2026 lessons learnt — EM26-16 Lessons Learnt</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>12_Lessons_Learnt/2026_EchoMind_Enterprise/EM26-16b_Lessons_Learnt_Logbook.docx</t>
+          <t>12_Lessons_Learnt/2026_EchoMind_Enterprise/EM26-16_Lessons_Learnt.docx</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>2026 lessons learnt — EM26-16 Lessons Learnt Log</t>
+          <t>2026 lessons learnt — EM26-16b Lessons Learnt Logbook</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>12_Lessons_Learnt/2026_EchoMind_Enterprise/EM26-16_Lessons_Learnt_Log.xlsx</t>
+          <t>12_Lessons_Learnt/2026_EchoMind_Enterprise/EM26-16b_Lessons_Learnt_Logbook.docx</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -3498,7 +3498,7 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>13_New_Use_Case_EchoMind</t>
+          <t>12_Lessons_Learnt</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
@@ -3508,22 +3508,22 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Capabilities of the five modules</t>
+          <t>2026 lessons learnt — EM26-16 Lessons Learnt Log</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>13_New_Use_Case_EchoMind/2026_EchoMind_Enterprise/CAPABILITIES.md</t>
+          <t>12_Lessons_Learnt/2026_EchoMind_Enterprise/EM26-16_Lessons_Learnt_Log.xlsx</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>docs</t>
+          <t>Evidence pack</t>
         </is>
       </c>
     </row>
@@ -3540,22 +3540,22 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>QASC 2026 paper — EchoMind architecture and results</t>
+          <t>Capabilities of the five modules</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>13_New_Use_Case_EchoMind/2026_EchoMind_Enterprise/EchoMind_QASC2026_CameraReady_v4.pdf</t>
+          <t>13_New_Use_Case_EchoMind/2026_EchoMind_Enterprise/CAPABILITIES.md</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>docs/paper</t>
+          <t>docs</t>
         </is>
       </c>
     </row>
@@ -3572,27 +3572,59 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
+          <t>QASC 2026 paper — EchoMind architecture and results</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>13_New_Use_Case_EchoMind/2026_EchoMind_Enterprise/EchoMind_QASC2026_CameraReady_v4.pdf</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>docs/paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>13_New_Use_Case_EchoMind</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>2026 EchoMind Enterprise</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
           <t>EM26-26 New Use Cases — EchoMind Enterprise</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr">
+      <c r="D101" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
+      <c r="E101" s="4" t="inlineStr">
         <is>
           <t>13_New_Use_Case_EchoMind/2026_EchoMind_Enterprise/EM26-26_New_Use_Cases_EchoMind_Enterprise.docx</t>
         </is>
       </c>
-      <c r="F100" s="4" t="inlineStr">
+      <c r="F101" s="4" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F100"/>
+  <autoFilter ref="A4:F101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/EchoMind_Audit_2026-10-14_Project2/00_Evidence_Index.xlsx
+++ b/docs/EchoMind_Audit_2026-10-14_Project2/00_Evidence_Index.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retrieve before the session" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evidence index'!$A$4:$F$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evidence index'!$A$4:$F$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Retrieve before the session'!$A$4:$C$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2474,32 +2474,32 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>08_Test_Plan_and_Test_Cases</t>
+          <t>07_Review_Records</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>2025 test case TC-EM-UI-Upload-001</t>
+          <t>EM26-33 Development, Review, Test and Release Process</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>07_Review_Records/EM26-33_Development_Review_Test_and_Release_Process.docx</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>2025 test case TC-EM-Stacks-002</t>
+          <t>2025 test case TC-EM-UI-Upload-001</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2025 test case TC-EM-Transcribe-003</t>
+          <t>2025 test case TC-EM-Stacks-002</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -2575,27 +2575,27 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>EM26-13 Acceptance criteria review</t>
+          <t>2025 test case TC-EM-Transcribe-003</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/EM26-13_Acceptance_Criteria_Review.docx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Evidence pack</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>13 acceptance test cases TC-EM-AUTH-101 … TC-EM-EVAL-114</t>
+          <t>EM26-13 Acceptance criteria review</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/Test_Cases</t>
+          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/EM26-13_Acceptance_Criteria_Review.docx</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -2644,22 +2644,22 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>SOP-07 Verification, validation and testing</t>
+          <t>13 acceptance test cases TC-EM-AUTH-101 … TC-EM-EVAL-114</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/procedures__SOP-07_Verification_Validation_and_Testing.docx</t>
+          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/Test_Cases</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>QMS</t>
+          <t>Evidence pack</t>
         </is>
       </c>
     </row>
@@ -2676,54 +2676,54 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>EM26-24 Test Plan — EchoMind Enterprise</t>
+          <t>SOP-07 Verification, validation and testing</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/EM26-24_Test_Plan_EchoMind_Enterprise.docx</t>
+          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/procedures__SOP-07_Verification_Validation_and_Testing.docx</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>QMS</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>09_Test_Reports</t>
+          <t>08_Test_Plan_and_Test_Cases</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>2025 test report — Failed Functional Test QA-FAIL-01</t>
+          <t>EM26-24 Test Plan — EchoMind Enterprise</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>08_Test_Plan_and_Test_Cases/2026_EchoMind_Enterprise/EM26-24_Test_Plan_EchoMind_Enterprise.docx</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>2025 test report — Defect Linking Jira DEF-2025-01</t>
+          <t>2025 test report — Failed Functional Test QA-FAIL-01</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>2025 test report — Regression Testing Defects REG-2025-01</t>
+          <t>2025 test report — Defect Linking Jira DEF-2025-01</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>2025 test report — AJACE Test Failure EchoMind</t>
+          <t>2025 test report — Regression Testing Defects REG-2025-01</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -2831,27 +2831,27 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Golden-question evaluation runs (24, 2026-07-29 → 09-22)</t>
+          <t>2025 test report — AJACE Test Failure EchoMind</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29 → 09-22</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>09_Test_Reports/2026_EchoMind_Enterprise/Golden_Suite_Runs</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/tree/main/eval/reports</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -2868,22 +2868,22 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>EM26-15 Test summary report</t>
+          <t>Golden-question evaluation runs (24, 2026-07-29 → 09-22)</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-07-29 → 09-22</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>09_Test_Reports/2026_EchoMind_Enterprise/EM26-15_Test_Summary_Report.docx</t>
+          <t>09_Test_Reports/2026_EchoMind_Enterprise/Golden_Suite_Runs</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Evidence pack</t>
+          <t>https://github.com/RW2523/echomind-enterprise/tree/main/eval/reports</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Acceptance test execution runs 1–4 (2026-10-06)</t>
+          <t>EM26-15 Test summary report</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>09_Test_Reports/2026_EchoMind_Enterprise/Execution_Records_run1-4</t>
+          <t>09_Test_Reports/2026_EchoMind_Enterprise/EM26-15_Test_Summary_Report.docx</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Failure → defect → regression records QA-FAIL-2026-01 … 07, DEF-2026-01, REG-2026-01</t>
+          <t>Acceptance test execution runs 1–4 (2026-10-06)</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>09_Test_Reports/2026_EchoMind_Enterprise/Failure_Defect_Regression</t>
+          <t>09_Test_Reports/2026_EchoMind_Enterprise/Execution_Records_run1-4</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -2964,86 +2964,86 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>CI runs and tickets</t>
+          <t>Failure → defect → regression records QA-FAIL-2026-01 … 07, DEF-2026-01, REG-2026-01</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>09_Test_Reports/2026_EchoMind_Enterprise/CI_Runs_and_Tickets</t>
+          <t>09_Test_Reports/2026_EchoMind_Enterprise/Failure_Defect_Regression</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>Evidence pack</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>10_Identification_and_Traceability</t>
+          <t>09_Test_Reports</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Appliance identification ‘EchoMind – university’ unit; UPS tracking; versioned Git</t>
+          <t>CI runs and tickets</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>09_Test_Reports/2026_EchoMind_Enterprise/CI_Runs_and_Tickets</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>GitHub</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>10_Identification_and_Traceability</t>
+          <t>09_Test_Reports</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>TC-EM-REL-106 Release identification test (pass, run 4)</t>
+          <t>EM26-34 Test Execution Register</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/TC-EM-REL-106_Release_identification_and_traceability.docx</t>
+          <t>09_Test_Reports/EM26-34_Test_Execution_Register.xlsx</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Evidence pack</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -3055,27 +3055,27 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>REG-08 Release and deployment register (versions v1.0.0 → v1.4.1, deployments)</t>
+          <t>Appliance identification ‘EchoMind – university’ unit; UPS tracking; versioned Git</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/registers__REG-08_Release_and_Deployment_Register.docx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/registers/REG-08_Release_and_Deployment_Register.md</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -3092,22 +3092,22 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Version tags v1.0.0 → v1.4.1 with their messages</t>
+          <t>TC-EM-REL-106 Release identification test (pass, run 4)</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/version_tags.txt</t>
+          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/TC-EM-REL-106_Release_identification_and_traceability.docx</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/tags</t>
+          <t>Evidence pack</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>EM26-20 › sheet ‘Traceability’ (requirement → review → commit → version → test → release)</t>
+          <t>REG-08 Release and deployment register (versions v1.0.0 → v1.4.1, deployments)</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/EM26-20_Functional_Requirements.xlsx</t>
+          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/registers__REG-08_Release_and_Deployment_Register.docx</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Controlled copy</t>
+          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/registers/REG-08_Release_and_Deployment_Register.md</t>
         </is>
       </c>
     </row>
@@ -3151,91 +3151,91 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>EM26-32 Identification and Traceability Record</t>
+          <t>Version tags v1.0.0 → v1.4.1 with their messages</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>10_Identification_and_Traceability/EM26-32_Identification_and_Traceability_Record.docx</t>
+          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/version_tags.txt</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>https://github.com/RW2523/echomind-enterprise/tags</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>11_Release_Notes</t>
+          <t>10_Identification_and_Traceability</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Final release package approved and released (MM-2025-09-01)</t>
+          <t>EM26-20 › sheet ‘Traceability’ (requirement → review → commit → version → test → release)</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>10_Identification_and_Traceability/2026_EchoMind_Enterprise/EM26-20_Functional_Requirements.xlsx</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>Controlled copy</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>11_Release_Notes</t>
+          <t>10_Identification_and_Traceability</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Release record (FRM-03) v1.4.0</t>
+          <t>EM26-32 Identification and Traceability Record</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>11_Release_Notes/2026_EchoMind_Enterprise/records__releases__2026-10-06_v1.4.0.docx</t>
+          <t>10_Identification_and_Traceability/EM26-32_Identification_and_Traceability_Record.docx</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/records/releases/2026-10-06_v1.4.0.md</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -3247,27 +3247,27 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>2026 EchoMind Enterprise</t>
+          <t>2025 University Project</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Release record (FRM-03) v1.4.1</t>
+          <t>Final release package approved and released (MM-2025-09-01)</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>11_Release_Notes/2026_EchoMind_Enterprise/records__releases__2026-10-06_v1.4.1.docx</t>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/records/releases/2026-10-06_v1.4.1.md</t>
+          <t>2025 evidence pack</t>
         </is>
       </c>
     </row>
@@ -3284,22 +3284,22 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>CHANGELOG — one section per version</t>
+          <t>Release record (FRM-03) v1.4.0</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>11_Release_Notes/2026_EchoMind_Enterprise/CHANGELOG.md</t>
+          <t>11_Release_Notes/2026_EchoMind_Enterprise/records__releases__2026-10-06_v1.4.0.docx</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>https://github.com/RW2523/echomind-enterprise/blob/main/CHANGELOG.md</t>
+          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/records/releases/2026-10-06_v1.4.0.md</t>
         </is>
       </c>
     </row>
@@ -3316,125 +3316,125 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>EM26-25 Release Notes v1.0.0 → v1.4.1</t>
+          <t>Release record (FRM-03) v1.4.1</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>11_Release_Notes/2026_EchoMind_Enterprise/EM26-25_Release_Notes_v1.0.0-v1.4.1.docx</t>
+          <t>11_Release_Notes/2026_EchoMind_Enterprise/records__releases__2026-10-06_v1.4.1.docx</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>https://github.com/RW2523/echomind-enterprise/blob/main/docs/qms/records/releases/2026-10-06_v1.4.1.md</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>12_Lessons_Learnt</t>
+          <t>11_Release_Notes</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>2025 lessons learnt — AJACE EchoMind Lessons Learned Log (May–Sep 2025)</t>
+          <t>CHANGELOG — one section per version</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>11_Release_Notes/2026_EchoMind_Enterprise/CHANGELOG.md</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>https://github.com/RW2523/echomind-enterprise/blob/main/CHANGELOG.md</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>12_Lessons_Learnt</t>
+          <t>11_Release_Notes</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>2025 lessons learnt — 16. AJACE_Lessons_Learnt_EchoMind</t>
+          <t>EM26-25 Release Notes v1.0.0 → v1.4.1</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>11_Release_Notes/2026_EchoMind_Enterprise/EM26-25_Release_Notes_v1.0.0-v1.4.1.docx</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>12_Lessons_Learnt</t>
+          <t>11_Release_Notes</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>2025 University Project</t>
+          <t>2026 EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>2025 lessons learnt — 16b. AJACE_Lessons_Learnt_Logbook_EchoMind</t>
+          <t>Release note v1.0.0 (2026-02-05 → 2026-02-27, 82 commits)</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+          <t>11_Release_Notes/Release_Notes_per_Version/Release_Note_v1.0.0.docx</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>2025 evidence pack</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>12_Lessons_Learnt</t>
+          <t>11_Release_Notes</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -3444,29 +3444,29 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>2026 lessons learnt — EM26-16 Lessons Learnt</t>
+          <t>Release note v1.1.0 (2026-03-03 → 2026-04-29, 32 commits)</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>12_Lessons_Learnt/2026_EchoMind_Enterprise/EM26-16_Lessons_Learnt.docx</t>
+          <t>11_Release_Notes/Release_Notes_per_Version/Release_Note_v1.1.0.docx</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Evidence pack</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>12_Lessons_Learnt</t>
+          <t>11_Release_Notes</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -3476,29 +3476,29 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>2026 lessons learnt — EM26-16b Lessons Learnt Logbook</t>
+          <t>Release note v1.2.0 (2026-05-27 → 2026-06-27, 44 commits)</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>12_Lessons_Learnt/2026_EchoMind_Enterprise/EM26-16b_Lessons_Learnt_Logbook.docx</t>
+          <t>11_Release_Notes/Release_Notes_per_Version/Release_Note_v1.2.0.docx</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Evidence pack</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>12_Lessons_Learnt</t>
+          <t>11_Release_Notes</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
@@ -3508,29 +3508,29 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>2026 lessons learnt — EM26-16 Lessons Learnt Log</t>
+          <t>Release note v1.3.0 (2026-07-16 → 2026-08-16, 39 commits)</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>12_Lessons_Learnt/2026_EchoMind_Enterprise/EM26-16_Lessons_Learnt_Log.xlsx</t>
+          <t>11_Release_Notes/Release_Notes_per_Version/Release_Note_v1.3.0.docx</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Evidence pack</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>13_New_Use_Case_EchoMind</t>
+          <t>11_Release_Notes</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -3540,29 +3540,29 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Capabilities of the five modules</t>
+          <t>Release note v1.4.0 (2026-09-04 → 2026-09-22, 9 commits)</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>13_New_Use_Case_EchoMind/2026_EchoMind_Enterprise/CAPABILITIES.md</t>
+          <t>11_Release_Notes/Release_Notes_per_Version/Release_Note_v1.4.0.docx</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>docs</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>13_New_Use_Case_EchoMind</t>
+          <t>11_Release_Notes</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
@@ -3572,59 +3572,315 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>QASC 2026 paper — EchoMind architecture and results</t>
+          <t>Release note v1.4.1 (2026-09-22 → 2026-10-06, 10 commits)</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>13_New_Use_Case_EchoMind/2026_EchoMind_Enterprise/EchoMind_QASC2026_CameraReady_v4.pdf</t>
+          <t>11_Release_Notes/Release_Notes_per_Version/Release_Note_v1.4.1.docx</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>docs/paper</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
+          <t>12_Lessons_Learnt</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>2025 University Project</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>2025 lessons learnt — AJACE EchoMind Lessons Learned Log (May–Sep 2025)</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>2025 evidence pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>12_Lessons_Learnt</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>2025 University Project</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>2025 lessons learnt — 16. AJACE_Lessons_Learnt_EchoMind</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>2025 evidence pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>12_Lessons_Learnt</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>2025 University Project</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>2025 lessons learnt — 16b. AJACE_Lessons_Learnt_Logbook_EchoMind</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>— held in the controlled copy (2025 original, names the 2025 customer)</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>2025 evidence pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>12_Lessons_Learnt</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>2026 EchoMind Enterprise</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>2026 lessons learnt — EM26-16 Lessons Learnt</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>12_Lessons_Learnt/2026_EchoMind_Enterprise/EM26-16_Lessons_Learnt.docx</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>Evidence pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>12_Lessons_Learnt</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>2026 EchoMind Enterprise</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>2026 lessons learnt — EM26-16b Lessons Learnt Logbook</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>12_Lessons_Learnt/2026_EchoMind_Enterprise/EM26-16b_Lessons_Learnt_Logbook.docx</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>Evidence pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>12_Lessons_Learnt</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>2026 EchoMind Enterprise</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>2026 lessons learnt — EM26-16 Lessons Learnt Log</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>12_Lessons_Learnt/2026_EchoMind_Enterprise/EM26-16_Lessons_Learnt_Log.xlsx</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>Evidence pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
           <t>13_New_Use_Case_EchoMind</t>
         </is>
       </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>2026 EchoMind Enterprise</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr">
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>2026 EchoMind Enterprise</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>Capabilities of the five modules</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>13_New_Use_Case_EchoMind/2026_EchoMind_Enterprise/CAPABILITIES.md</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>13_New_Use_Case_EchoMind</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>2026 EchoMind Enterprise</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>QASC 2026 paper — EchoMind architecture and results</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>13_New_Use_Case_EchoMind/2026_EchoMind_Enterprise/EchoMind_QASC2026_CameraReady_v4.pdf</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>docs/paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>13_New_Use_Case_EchoMind</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>2026 EchoMind Enterprise</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
         <is>
           <t>EM26-26 New Use Cases — EchoMind Enterprise</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr">
+      <c r="D109" s="4" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
+      <c r="E109" s="4" t="inlineStr">
         <is>
           <t>13_New_Use_Case_EchoMind/2026_EchoMind_Enterprise/EM26-26_New_Use_Cases_EchoMind_Enterprise.docx</t>
         </is>
       </c>
-      <c r="F101" s="4" t="inlineStr">
+      <c r="F109" s="4" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F101"/>
+  <autoFilter ref="A4:F109"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
